--- a/InputFiles/ICDC/TC28_ICDC_COTC021_Breed-GermnShphrdDog.xlsx
+++ b/InputFiles/ICDC/TC28_ICDC_COTC021_Breed-GermnShphrdDog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/epishinavv/git/Commons_Automation/InputFiles/ICDC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4067D8C2-01FB-A44A-BBEA-DE4E7FCF8F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E58CAB7-85E0-DA46-9502-7AD7C36A38A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView xWindow="36000" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 JOIN 
     df_enrollment enr ON enr."case.case_record_id" = c.case_record_id
 JOIN 
-    df_sample smp ON smp."case.case_record_id" = c.case_record_id
+    df_sample smp ON smp."case.case_id" = c.case_record_id
 LEFT JOIN 
     df_case_file cf ON cf."sample.sample_id" = smp.sample_id
 LEFT JOIN 
@@ -153,7 +153,7 @@
 FROM 
     df_sample smp
 JOIN 
-    df_case c ON smp."case.case_record_id" = c.case_record_id
+    df_case c ON smp."case.case_id" = c.case_record_id
 JOIN 
     df_publication pub ON pub."study.clinical_study_designation" = st.clinical_study_designation
 JOIN 
@@ -229,7 +229,7 @@
 JOIN 
     df_sample smp ON cf."sample.sample_id" = smp.sample_id
 JOIN 
-    df_case c ON smp."case.case_record_id" = c.case_record_id
+    df_case c ON smp."case.case_id" = c.case_record_id
 JOIN 
     df_study st ON c."study.clinical_study_designation" = st.clinical_study_designation
 JOIN 
@@ -262,6 +262,7 @@
         WHEN cf.file_name LIKE '%.fastq.gz' THEN 'fastq'
         WHEN cf.file_name LIKE '%.vcf.gz' THEN 'vcf'
         WHEN cf.file_name LIKE '%.tsv.gz' THEN 'tsv'
+        WHEN cf.file_name LIKE '%.txt.gz' THEN 'txt'
         WHEN cf.file_name LIKE '%.pdf' THEN 'pdf'
         WHEN cf.file_name LIKE '%.rtf' THEN 'rtf'
         WHEN cf.file_name LIKE '%.tbi' THEN 'tbi'
@@ -311,7 +312,7 @@
 JOIN 
     df_sample smp ON cf."sample.sample_id" = smp.sample_id
 JOIN 
-    df_case c ON smp."case.case_record_id" = c.case_record_id
+    df_case c ON smp."case.case_id" = c.case_record_id
 JOIN 
     df_study st ON c."study.clinical_study_designation" = st.clinical_study_designation
 JOIN 
@@ -337,9 +338,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -399,11 +407,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -763,7 +774,7 @@
       <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D2" t="s">
@@ -786,7 +797,7 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="2"/>
@@ -804,7 +815,7 @@
       <c r="C6" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
